--- a/docs/etudes/data/etude-2026-08-03.xlsx
+++ b/docs/etudes/data/etude-2026-08-03.xlsx
@@ -2662,75 +2662,75 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Phra Khanong</t>
+          <t>Bang Sue</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>82812</v>
       </c>
       <c r="C20" t="n">
-        <v>428.6</v>
+        <v>369.3</v>
       </c>
       <c r="D20" t="n">
-        <v>5.59</v>
+        <v>5.44</v>
       </c>
       <c r="E20" t="n">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="F20" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="G20" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>83548</v>
+        <v>115929</v>
       </c>
       <c r="L20" t="n">
-        <v>4.63</v>
+        <v>3.8</v>
       </c>
       <c r="M20" t="n">
-        <v>5.04</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bang Sue</t>
+          <t>Phra Khanong</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>82812</v>
       </c>
       <c r="C21" t="n">
-        <v>369.3</v>
+        <v>428.6</v>
       </c>
       <c r="D21" t="n">
-        <v>5.44</v>
+        <v>5.59</v>
       </c>
       <c r="E21" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="G21" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>115929</v>
+        <v>83548</v>
       </c>
       <c r="L21" t="n">
-        <v>3.8</v>
+        <v>4.63</v>
       </c>
       <c r="M21" t="n">
-        <v>1.32</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="22">
